--- a/software/curves/3. Final Round/X018_LM/curve_0.0_3_Reverse.xlsx
+++ b/software/curves/3. Final Round/X018_LM/curve_0.0_3_Reverse.xlsx
@@ -1,21 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Walker Arce\Documents\GitHub\Perovskite-Curve-Tracer\software\curves\3. Final Round\X018_LM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4806C719-3103-468F-9C12-B36554D9C9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>Time</t>
   </si>
@@ -76,15 +95,27 @@
   <si>
     <t>Power</t>
   </si>
+  <si>
+    <t>Jsc</t>
+  </si>
+  <si>
+    <t>PCE</t>
+  </si>
+  <si>
+    <t>Pmax</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,6 +131,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -109,7 +147,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -132,29 +170,56 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -192,7 +257,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -226,6 +291,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -260,9 +326,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -435,24 +502,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B1" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2">
-        <v>45215.64703340166</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>45215.647033401663</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -460,7 +527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -468,15 +535,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0.058</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>5.8000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -484,7 +551,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -492,15 +559,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0.004820512820512821</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>4.8205128205128208E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -508,15 +575,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0.7616410256410256</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>0.76164102564102565</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -524,31 +591,31 @@
         <v>1.189374895257248</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0.9058767150954179</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>0.90587671509541789</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B13">
-        <v>9058767.150954179</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>9058767.1509541795</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0.1561856405336927</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>0.15618564053369269</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -562,11 +629,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E257"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:L257"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
@@ -579,297 +649,357 @@
       <c r="E1" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.004820512820512821</v>
+        <v>4.8205128205128208E-3</v>
       </c>
       <c r="C2">
         <v>1.378414613708731</v>
       </c>
       <c r="D2">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E2">
-        <v>0.006644665317365166</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>6.6446653173651664E-3</v>
+      </c>
+      <c r="F2" s="6">
+        <v>45215</v>
+      </c>
+      <c r="G2" s="4">
+        <f>MAX(E2:E257)/(C2*B234)</f>
+        <v>0.67379618733819746</v>
+      </c>
+      <c r="H2" s="7">
+        <f>MAX(B2:B257)</f>
+        <v>0.97535042735042732</v>
+      </c>
+      <c r="I2" s="8">
+        <f>MAX(D2:D257)</f>
+        <v>23.765769201874679</v>
+      </c>
+      <c r="J2" s="5">
+        <f>(L2/100)</f>
+        <v>0.15618564053369274</v>
+      </c>
+      <c r="K2">
+        <f>MAX(C2:C257)</f>
+        <v>1.378414613708731</v>
+      </c>
+      <c r="L2">
+        <f>(H2*K2*G2)/0.058</f>
+        <v>15.618564053369274</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.006427350427350428</v>
+        <v>6.4273504273504277E-3</v>
       </c>
       <c r="C3">
         <v>1.378414613708731</v>
       </c>
       <c r="D3">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E3">
-        <v>0.008859553756486888</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>8.8595537564868879E-3</v>
+      </c>
+      <c r="F3" s="6">
+        <v>45177</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.74299999999999999</v>
+      </c>
+      <c r="H3">
+        <v>1.095</v>
+      </c>
+      <c r="I3">
+        <v>22.5</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0.184</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.008034188034188034</v>
+        <v>8.0341880341880337E-3</v>
       </c>
       <c r="C4">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D4">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E4">
-        <v>0.01101115966877656</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>1.101115966877656E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0.009641025641025642</v>
+        <v>9.6410256410256415E-3</v>
       </c>
       <c r="C5">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D5">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E5">
-        <v>0.01321339160253187</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>1.321339160253187E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0.01285470085470086</v>
+        <v>1.2854700854700861E-2</v>
       </c>
       <c r="C6">
         <v>1.378414613708731</v>
       </c>
       <c r="D6">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E6">
-        <v>0.01771910751297378</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>1.7719107512973779E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0.01767521367521368</v>
+        <v>1.7675213675213679E-2</v>
       </c>
       <c r="C7">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D7">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E7">
-        <v>0.02422455127130843</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>2.4224551271308431E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0.02088888888888889</v>
+        <v>2.0888888888888891E-2</v>
       </c>
       <c r="C8">
         <v>1.378414613708731</v>
       </c>
       <c r="D8">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E8">
-        <v>0.02879354970858239</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>2.8793549708582389E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0.02570940170940171</v>
+        <v>2.5709401709401711E-2</v>
       </c>
       <c r="C9">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D9">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E9">
-        <v>0.035235710940085</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>3.5235710940084999E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0.03213675213675213</v>
+        <v>3.2136752136752128E-2</v>
       </c>
       <c r="C10">
         <v>1.378414613708731</v>
       </c>
       <c r="D10">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E10">
-        <v>0.04429776878243444</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>4.4297768782434438E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0.03856410256410257</v>
+        <v>3.8564102564102573E-2</v>
       </c>
       <c r="C11">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D11">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E11">
-        <v>0.0528535664101275</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>5.2853566410127499E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0.0465982905982906</v>
+        <v>4.6598290598290598E-2</v>
       </c>
       <c r="C12">
         <v>1.378414613708731</v>
       </c>
       <c r="D12">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E12">
-        <v>0.06423176473452993</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>6.4231764734529934E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0.05463247863247863</v>
+        <v>5.463247863247863E-2</v>
       </c>
       <c r="C13">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D13">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E13">
-        <v>0.07487588574768062</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>7.4875885747680615E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0.06105982905982906</v>
+        <v>6.1059829059829061E-2</v>
       </c>
       <c r="C14">
         <v>1.378414613708731</v>
       </c>
       <c r="D14">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E14">
-        <v>0.08416576068662543</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>8.4165760686625429E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15">
-        <v>0.06748717948717949</v>
+        <v>6.7487179487179486E-2</v>
       </c>
       <c r="C15">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D15">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E15">
-        <v>0.09249374121772312</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>9.2493741217723122E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16">
-        <v>0.07391452991452992</v>
+        <v>7.3914529914529917E-2</v>
       </c>
       <c r="C16">
         <v>1.378414613708731</v>
       </c>
       <c r="D16">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E16">
         <v>0.1018848681995992</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17">
-        <v>0.08034188034188035</v>
+        <v>8.0341880341880348E-2</v>
       </c>
       <c r="C17">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D17">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E17">
         <v>0.1101115966877656</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18">
-        <v>0.0931965811965812</v>
+        <v>9.3196581196581196E-2</v>
       </c>
       <c r="C18">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D18">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E18">
-        <v>0.1277294521578081</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>0.12772945215780809</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -877,16 +1007,16 @@
         <v>0.1060512820512821</v>
       </c>
       <c r="C19">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D19">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E19">
-        <v>0.1453473076278506</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>0.14534730762785061</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -894,50 +1024,50 @@
         <v>0.1172991452991453</v>
       </c>
       <c r="C20">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D20">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E20">
-        <v>0.1607629311641378</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>0.16076293116413781</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21">
-        <v>0.126940170940171</v>
+        <v>0.12694017094017099</v>
       </c>
       <c r="C21">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D21">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E21">
-        <v>0.1739763227666697</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>0.17397632276666969</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22">
-        <v>0.1365811965811966</v>
+        <v>0.13658119658119661</v>
       </c>
       <c r="C22">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D22">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E22">
-        <v>0.1871897143692015</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>0.18718971436920151</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -945,50 +1075,50 @@
         <v>0.1462222222222222</v>
       </c>
       <c r="C23">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D23">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E23">
-        <v>0.2004031059717334</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>0.20040310597173339</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24">
-        <v>0.1542564102564103</v>
+        <v>0.15425641025641029</v>
       </c>
       <c r="C24">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D24">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E24">
         <v>0.21141426564051</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25">
-        <v>0.1638974358974359</v>
+        <v>0.16389743589743591</v>
       </c>
       <c r="C25">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D25">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E25">
-        <v>0.2246276572430418</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>0.22462765724304179</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -996,16 +1126,16 @@
         <v>0.1735384615384615</v>
       </c>
       <c r="C26">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D26">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E26">
-        <v>0.2378410488455737</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>0.23784104884557369</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -1013,16 +1143,16 @@
         <v>0.1831794871794872</v>
       </c>
       <c r="C27">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D27">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E27">
         <v>0.2510544404481056</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1030,84 +1160,84 @@
         <v>0.1928205128205128</v>
       </c>
       <c r="C28">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D28">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E28">
-        <v>0.2642678320506375</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>0.26426783205063747</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>27</v>
       </c>
       <c r="B29">
-        <v>0.2008547008547009</v>
+        <v>0.20085470085470089</v>
       </c>
       <c r="C29">
         <v>1.378414613708731</v>
       </c>
       <c r="D29">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E29">
-        <v>0.2768610548902152</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>0.27686105489021517</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>28</v>
       </c>
       <c r="B30">
-        <v>0.2104957264957265</v>
+        <v>0.21049572649572651</v>
       </c>
       <c r="C30">
         <v>1.378414613708731</v>
       </c>
       <c r="D30">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E30">
         <v>0.2901503855249456</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>29</v>
       </c>
       <c r="B31">
-        <v>0.2185299145299145</v>
+        <v>0.21852991452991449</v>
       </c>
       <c r="C31">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D31">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E31">
-        <v>0.2995035429907225</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>0.29950354299072252</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>30</v>
       </c>
       <c r="B32">
-        <v>0.2265641025641026</v>
+        <v>0.22656410256410259</v>
       </c>
       <c r="C32">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D32">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E32">
-        <v>0.310514702659499</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>0.31051470265949899</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -1115,441 +1245,441 @@
         <v>0.2345982905982906</v>
       </c>
       <c r="C33">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D33">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E33">
-        <v>0.3215258623282756</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>0.32152586232827562</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>32</v>
       </c>
       <c r="B34">
-        <v>0.2522735042735043</v>
+        <v>0.25227350427350431</v>
       </c>
       <c r="C34">
         <v>1.378414613708731</v>
       </c>
       <c r="D34">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E34">
-        <v>0.3477374849421103</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>0.34773748494211032</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>33</v>
       </c>
       <c r="B35">
-        <v>0.2715555555555556</v>
+        <v>0.27155555555555561</v>
       </c>
       <c r="C35">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D35">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E35">
-        <v>0.3721771968046478</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>0.37217719680464778</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>34</v>
       </c>
       <c r="B36">
-        <v>0.286017094017094</v>
+        <v>0.28601709401709402</v>
       </c>
       <c r="C36">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D36">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E36">
         <v>0.3919972842084456</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>35</v>
       </c>
       <c r="B37">
-        <v>0.3004786324786325</v>
+        <v>0.30047863247863249</v>
       </c>
       <c r="C37">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D37">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E37">
-        <v>0.4118173716122434</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>0.41181737161224341</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>36</v>
       </c>
       <c r="B38">
-        <v>0.314940170940171</v>
+        <v>0.31494017094017102</v>
       </c>
       <c r="C38">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D38">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E38">
-        <v>0.4316374590160412</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>0.43163745901604123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>37</v>
       </c>
       <c r="B39">
-        <v>0.3261880341880342</v>
+        <v>0.32618803418803421</v>
       </c>
       <c r="C39">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D39">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E39">
-        <v>0.4470530825523285</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>0.44705308255232851</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>38</v>
       </c>
       <c r="B40">
-        <v>0.3374358974358974</v>
+        <v>0.33743589743589741</v>
       </c>
       <c r="C40">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D40">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E40">
-        <v>0.4624687060886156</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>0.46246870608861562</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>39</v>
       </c>
       <c r="B41">
-        <v>0.3486837606837607</v>
+        <v>0.34868376068376072</v>
       </c>
       <c r="C41">
         <v>1.362661303837774</v>
       </c>
       <c r="D41">
-        <v>23.49416041099611</v>
+        <v>23.494160410996109</v>
       </c>
       <c r="E41">
-        <v>0.4751378679603919</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>0.47513786796039192</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>40</v>
       </c>
       <c r="B42">
-        <v>0.3599316239316239</v>
+        <v>0.35993162393162392</v>
       </c>
       <c r="C42">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D42">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E42">
-        <v>0.49329995316119</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>0.49329995316119002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>41</v>
       </c>
       <c r="B43">
-        <v>0.3711794871794872</v>
+        <v>0.37117948717948718</v>
       </c>
       <c r="C43">
         <v>1.362661303837774</v>
       </c>
       <c r="D43">
-        <v>23.49416041099611</v>
+        <v>23.494160410996109</v>
       </c>
       <c r="E43">
-        <v>0.5057919239578365</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>0.50579192395783645</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>42</v>
       </c>
       <c r="B44">
-        <v>0.3824273504273504</v>
+        <v>0.38242735042735038</v>
       </c>
       <c r="C44">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D44">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E44">
-        <v>0.5241312002337644</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>0.52413120023376436</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>43</v>
       </c>
       <c r="B45">
-        <v>0.3920683760683761</v>
+        <v>0.39206837606837608</v>
       </c>
       <c r="C45">
         <v>1.362661303837774</v>
       </c>
       <c r="D45">
-        <v>23.49416041099611</v>
+        <v>23.494160410996109</v>
       </c>
       <c r="E45">
-        <v>0.5342564045268922</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>0.53425640452689216</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>44</v>
       </c>
       <c r="B46">
-        <v>0.4017094017094017</v>
+        <v>0.40170940170940173</v>
       </c>
       <c r="C46">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D46">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E46">
-        <v>0.5505579834388281</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>0.55055798343882811</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>45</v>
       </c>
       <c r="B47">
-        <v>0.4097435897435898</v>
+        <v>0.40974358974358982</v>
       </c>
       <c r="C47">
         <v>1.362661303837774</v>
       </c>
       <c r="D47">
-        <v>23.49416041099611</v>
+        <v>23.494160410996109</v>
       </c>
       <c r="E47">
-        <v>0.5583417342391701</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>0.55834173423917011</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>46</v>
       </c>
       <c r="B48">
-        <v>0.4193846153846154</v>
+        <v>0.41938461538461541</v>
       </c>
       <c r="C48">
         <v>1.362661303837774</v>
       </c>
       <c r="D48">
-        <v>23.49416041099611</v>
+        <v>23.494160410996109</v>
       </c>
       <c r="E48">
         <v>0.5714791868095036</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>47</v>
       </c>
       <c r="B49">
-        <v>0.4274188034188034</v>
+        <v>0.42741880341880339</v>
       </c>
       <c r="C49">
         <v>1.362661303837774</v>
       </c>
       <c r="D49">
-        <v>23.49416041099611</v>
+        <v>23.494160410996109</v>
       </c>
       <c r="E49">
-        <v>0.5824270639514481</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>0.58242706395144805</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>48</v>
       </c>
       <c r="B50">
-        <v>0.4402735042735043</v>
+        <v>0.44027350427350431</v>
       </c>
       <c r="C50">
         <v>1.362661303837774</v>
       </c>
       <c r="D50">
-        <v>23.49416041099611</v>
+        <v>23.494160410996109</v>
       </c>
       <c r="E50">
-        <v>0.5999436673785593</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>0.59994366737855931</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>49</v>
       </c>
       <c r="B51">
-        <v>0.4531282051282051</v>
+        <v>0.45312820512820512</v>
       </c>
       <c r="C51">
         <v>1.362661303837774</v>
       </c>
       <c r="D51">
-        <v>23.49416041099611</v>
+        <v>23.494160410996109</v>
       </c>
       <c r="E51">
-        <v>0.6174602708056705</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+        <v>0.61746027080567045</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>50</v>
       </c>
       <c r="B52">
-        <v>0.4643760683760684</v>
+        <v>0.46437606837606837</v>
       </c>
       <c r="C52">
         <v>1.362661303837774</v>
       </c>
       <c r="D52">
-        <v>23.49416041099611</v>
+        <v>23.494160410996109</v>
       </c>
       <c r="E52">
-        <v>0.6327872988043929</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+        <v>0.63278729880439288</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>51</v>
       </c>
       <c r="B53">
-        <v>0.4756239316239316</v>
+        <v>0.47562393162393157</v>
       </c>
       <c r="C53">
         <v>1.362661303837774</v>
       </c>
       <c r="D53">
-        <v>23.49416041099611</v>
+        <v>23.494160410996109</v>
       </c>
       <c r="E53">
-        <v>0.6481143268031151</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <v>0.64811432680311509</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>52</v>
       </c>
       <c r="B54">
-        <v>0.4852649572649573</v>
+        <v>0.48526495726495728</v>
       </c>
       <c r="C54">
         <v>1.362661303837774</v>
       </c>
       <c r="D54">
-        <v>23.49416041099611</v>
+        <v>23.494160410996109</v>
       </c>
       <c r="E54">
-        <v>0.6612517793734486</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>0.66125177937344859</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>53</v>
       </c>
       <c r="B55">
-        <v>0.4949059829059829</v>
+        <v>0.49490598290598292</v>
       </c>
       <c r="C55">
-        <v>1.354784648902296</v>
+        <v>1.3547846489022961</v>
       </c>
       <c r="D55">
-        <v>23.35835601555682</v>
+        <v>23.358356015556819</v>
       </c>
       <c r="E55">
-        <v>0.6704910282909277</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>0.67049102829092766</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>54</v>
       </c>
       <c r="B56">
-        <v>0.502940170940171</v>
+        <v>0.50294017094017096</v>
       </c>
       <c r="C56">
-        <v>1.354784648902296</v>
+        <v>1.3547846489022961</v>
       </c>
       <c r="D56">
-        <v>23.35835601555682</v>
+        <v>23.358356015556819</v>
       </c>
       <c r="E56">
-        <v>0.68137562290604</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>0.68137562290604003</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>55</v>
       </c>
       <c r="B57">
-        <v>0.5125811965811966</v>
+        <v>0.51258119658119661</v>
       </c>
       <c r="C57">
-        <v>1.354784648902296</v>
+        <v>1.3547846489022961</v>
       </c>
       <c r="D57">
-        <v>23.35835601555682</v>
+        <v>23.358356015556819</v>
       </c>
       <c r="E57">
-        <v>0.694437136444175</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <v>0.69443713644417504</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>56</v>
       </c>
       <c r="B58">
-        <v>0.5222222222222223</v>
+        <v>0.52222222222222225</v>
       </c>
       <c r="C58">
         <v>1.346907993966818</v>
       </c>
       <c r="D58">
-        <v>23.22255162011754</v>
+        <v>23.222551620117539</v>
       </c>
       <c r="E58">
-        <v>0.703385285738227</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>0.70338528573822701</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -1560,523 +1690,523 @@
         <v>1.346907993966818</v>
       </c>
       <c r="D59">
-        <v>23.22255162011754</v>
+        <v>23.222551620117539</v>
       </c>
       <c r="E59">
-        <v>0.7163708602441635</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <v>0.71637086024416352</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>58</v>
       </c>
       <c r="B60">
-        <v>0.5398974358974359</v>
+        <v>0.53989743589743588</v>
       </c>
       <c r="C60">
         <v>1.346907993966818</v>
       </c>
       <c r="D60">
-        <v>23.22255162011754</v>
+        <v>23.222551620117539</v>
       </c>
       <c r="E60">
-        <v>0.7271921723324438</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>0.72719217233244382</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>59</v>
       </c>
       <c r="B61">
-        <v>0.5495384615384615</v>
+        <v>0.54953846153846153</v>
       </c>
       <c r="C61">
         <v>1.346907993966818</v>
       </c>
       <c r="D61">
-        <v>23.22255162011754</v>
+        <v>23.222551620117539</v>
       </c>
       <c r="E61">
-        <v>0.7401777468383803</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+        <v>0.74017774683838033</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>60</v>
       </c>
       <c r="B62">
-        <v>0.555965811965812</v>
+        <v>0.55596581196581196</v>
       </c>
       <c r="C62">
         <v>1.346907993966818</v>
       </c>
       <c r="D62">
-        <v>23.22255162011754</v>
+        <v>23.222551620117539</v>
       </c>
       <c r="E62">
-        <v>0.7488347965090048</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+        <v>0.74883479650900475</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>61</v>
       </c>
       <c r="B63">
-        <v>0.5656068376068376</v>
+        <v>0.56560683760683761</v>
       </c>
       <c r="C63">
-        <v>1.339031339031339</v>
+        <v>1.3390313390313391</v>
       </c>
       <c r="D63">
-        <v>23.08674722467826</v>
+        <v>23.086747224678259</v>
       </c>
       <c r="E63">
         <v>0.7573652811259648</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>62</v>
       </c>
       <c r="B64">
-        <v>0.572034188034188</v>
+        <v>0.57203418803418804</v>
       </c>
       <c r="C64">
-        <v>1.339031339031339</v>
+        <v>1.3390313390313391</v>
       </c>
       <c r="D64">
-        <v>23.08674722467826</v>
+        <v>23.086747224678259</v>
       </c>
       <c r="E64">
-        <v>0.7659717047751234</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>0.76597170477512344</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>63</v>
       </c>
       <c r="B65">
-        <v>0.5800683760683761</v>
+        <v>0.58006837606837613</v>
       </c>
       <c r="C65">
-        <v>1.339031339031339</v>
+        <v>1.3390313390313391</v>
       </c>
       <c r="D65">
-        <v>23.08674722467826</v>
+        <v>23.086747224678259</v>
       </c>
       <c r="E65">
-        <v>0.7767297343365719</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+        <v>0.77672973433657189</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>64</v>
       </c>
       <c r="B66">
-        <v>0.5913162393162393</v>
+        <v>0.59131623931623933</v>
       </c>
       <c r="C66">
         <v>1.331154684095861</v>
       </c>
       <c r="D66">
-        <v>22.95094282923898</v>
+        <v>22.950942829238979</v>
       </c>
       <c r="E66">
-        <v>0.7871333817477608</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+        <v>0.78713338174776082</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>65</v>
       </c>
       <c r="B67">
-        <v>0.600957264957265</v>
+        <v>0.60095726495726498</v>
       </c>
       <c r="C67">
         <v>1.331154684095861</v>
       </c>
       <c r="D67">
-        <v>22.95094282923898</v>
+        <v>22.950942829238979</v>
       </c>
       <c r="E67">
-        <v>0.7999670781893005</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
+        <v>0.79996707818930046</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>66</v>
       </c>
       <c r="B68">
-        <v>0.6089914529914531</v>
+        <v>0.60899145299145307</v>
       </c>
       <c r="C68">
-        <v>1.323278029160382</v>
+        <v>1.3232780291603821</v>
       </c>
       <c r="D68">
-        <v>22.81513843379969</v>
+        <v>22.815138433799689</v>
       </c>
       <c r="E68">
-        <v>0.8058650096900475</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+        <v>0.80586500969004748</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>67</v>
       </c>
       <c r="B69">
-        <v>0.6186324786324787</v>
+        <v>0.61863247863247872</v>
       </c>
       <c r="C69">
         <v>1.315401374224904</v>
       </c>
       <c r="D69">
-        <v>22.67933403836041</v>
+        <v>22.679334038360409</v>
       </c>
       <c r="E69">
         <v>0.8137500125333208</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>68</v>
       </c>
       <c r="B70">
-        <v>0.6266666666666666</v>
+        <v>0.62666666666666659</v>
       </c>
       <c r="C70">
         <v>1.315401374224904</v>
       </c>
       <c r="D70">
-        <v>22.67933403836041</v>
+        <v>22.679334038360409</v>
       </c>
       <c r="E70">
         <v>0.8243181945142728</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>69</v>
       </c>
       <c r="B71">
-        <v>0.6347008547008547</v>
+        <v>0.63470085470085469</v>
       </c>
       <c r="C71">
         <v>1.307524719289425</v>
       </c>
       <c r="D71">
-        <v>22.54352964292112</v>
+        <v>22.543529642921118</v>
       </c>
       <c r="E71">
-        <v>0.8298870568754931</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+        <v>0.82988705687549313</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>70</v>
       </c>
       <c r="B72">
-        <v>0.6427350427350428</v>
+        <v>0.64273504273504278</v>
       </c>
       <c r="C72">
         <v>1.307524719289425</v>
       </c>
       <c r="D72">
-        <v>22.54352964292112</v>
+        <v>22.543529642921118</v>
       </c>
       <c r="E72">
-        <v>0.8403919563296134</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>0.84039195632961339</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>71</v>
       </c>
       <c r="B73">
-        <v>0.6491623931623932</v>
+        <v>0.64916239316239321</v>
       </c>
       <c r="C73">
         <v>1.299648064353947</v>
       </c>
       <c r="D73">
-        <v>22.40772524748184</v>
+        <v>22.407725247481839</v>
       </c>
       <c r="E73">
-        <v>0.8436826477248801</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+        <v>0.84368264772488011</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>72</v>
       </c>
       <c r="B74">
-        <v>0.6571965811965813</v>
+        <v>0.65719658119658131</v>
       </c>
       <c r="C74">
         <v>1.299648064353947</v>
       </c>
       <c r="D74">
-        <v>22.40772524748184</v>
+        <v>22.407725247481839</v>
       </c>
       <c r="E74">
-        <v>0.8541242646521683</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+        <v>0.85412426465216829</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>73</v>
       </c>
       <c r="B75">
-        <v>0.6652307692307692</v>
+        <v>0.66523076923076918</v>
       </c>
       <c r="C75">
         <v>1.291771409418468</v>
       </c>
       <c r="D75">
-        <v>22.27192085204256</v>
+        <v>22.271920852042559</v>
       </c>
       <c r="E75">
         <v>0.8593260883577627</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>74</v>
       </c>
       <c r="B76">
-        <v>0.6716581196581197</v>
+        <v>0.67165811965811972</v>
       </c>
       <c r="C76">
         <v>1.28389475448299</v>
       </c>
       <c r="D76">
-        <v>22.13611645660327</v>
+        <v>22.136116456603268</v>
       </c>
       <c r="E76">
-        <v>0.8623383366349682</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+        <v>0.86233833663496817</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>75</v>
       </c>
       <c r="B77">
-        <v>0.6780854700854702</v>
+        <v>0.67808547008547015</v>
       </c>
       <c r="C77">
         <v>1.28389475448299</v>
       </c>
       <c r="D77">
-        <v>22.13611645660327</v>
+        <v>22.136116456603268</v>
       </c>
       <c r="E77">
-        <v>0.8705903781338674</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+        <v>0.87059037813386742</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>76</v>
       </c>
       <c r="B78">
-        <v>0.6845128205128205</v>
+        <v>0.68451282051282047</v>
       </c>
       <c r="C78">
         <v>1.276018099547511</v>
       </c>
       <c r="D78">
-        <v>22.00031206116399</v>
+        <v>22.000312061163989</v>
       </c>
       <c r="E78">
         <v>0.8734507483466758</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>77</v>
       </c>
       <c r="B79">
-        <v>0.690940170940171</v>
+        <v>0.69094017094017102</v>
       </c>
       <c r="C79">
         <v>1.276018099547511</v>
       </c>
       <c r="D79">
-        <v>22.00031206116399</v>
+        <v>22.000312061163989</v>
       </c>
       <c r="E79">
         <v>0.8816521638241096</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>78</v>
       </c>
       <c r="B80">
-        <v>0.6957606837606838</v>
+        <v>0.69576068376068378</v>
       </c>
       <c r="C80">
-        <v>1.268141444612033</v>
+        <v>1.2681414446120329</v>
       </c>
       <c r="D80">
-        <v>21.86450766572471</v>
+        <v>21.864507665724709</v>
       </c>
       <c r="E80">
-        <v>0.8823229586085294</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <v>0.88232295860852938</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>79</v>
       </c>
       <c r="B81">
-        <v>0.7005811965811966</v>
+        <v>0.70058119658119655</v>
       </c>
       <c r="C81">
-        <v>1.268141444612033</v>
+        <v>1.2681414446120329</v>
       </c>
       <c r="D81">
-        <v>21.86450766572471</v>
+        <v>21.864507665724709</v>
       </c>
       <c r="E81">
-        <v>0.8884360507005052</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+        <v>0.88843605070050524</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>80</v>
       </c>
       <c r="B82">
-        <v>0.7086153846153846</v>
+        <v>0.70861538461538465</v>
       </c>
       <c r="C82">
-        <v>1.252388134741076</v>
+        <v>1.2523881347410759</v>
       </c>
       <c r="D82">
-        <v>21.59289887484614</v>
+        <v>21.592898874846139</v>
       </c>
       <c r="E82">
-        <v>0.8874614997872917</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <v>0.88746149978729172</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>81</v>
       </c>
       <c r="B83">
-        <v>0.715042735042735</v>
+        <v>0.71504273504273497</v>
       </c>
       <c r="C83">
-        <v>1.244511479805598</v>
+        <v>1.2445114798055981</v>
       </c>
       <c r="D83">
-        <v>21.45709447940686</v>
+        <v>21.457094479406859</v>
       </c>
       <c r="E83">
         <v>0.8898788923122759</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>82</v>
       </c>
       <c r="B84">
-        <v>0.7214700854700855</v>
+        <v>0.72147008547008551</v>
       </c>
       <c r="C84">
-        <v>1.236634824870119</v>
+        <v>1.2366348248701191</v>
       </c>
       <c r="D84">
-        <v>21.32129008396756</v>
+        <v>21.321290083967561</v>
       </c>
       <c r="E84">
-        <v>0.8921950327943288</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+        <v>0.89219503279432877</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>83</v>
       </c>
       <c r="B85">
-        <v>0.7278974358974359</v>
+        <v>0.72789743589743594</v>
       </c>
       <c r="C85">
         <v>1.228758169934641</v>
       </c>
       <c r="D85">
-        <v>21.18548568852828</v>
+        <v>21.185485688528281</v>
       </c>
       <c r="E85">
-        <v>0.8944099212334508</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+        <v>0.89440992123345076</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>84</v>
       </c>
       <c r="B86">
-        <v>0.7327179487179487</v>
+        <v>0.73271794871794871</v>
       </c>
       <c r="C86">
         <v>1.228758169934641</v>
       </c>
       <c r="D86">
-        <v>21.18548568852828</v>
+        <v>21.185485688528281</v>
       </c>
       <c r="E86">
         <v>0.9003331657449305</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>85</v>
       </c>
       <c r="B87">
-        <v>0.7375384615384616</v>
+        <v>0.73753846153846159</v>
       </c>
       <c r="C87">
         <v>1.213004860063684</v>
       </c>
       <c r="D87">
-        <v>20.91387689764971</v>
+        <v>20.913876897649711</v>
       </c>
       <c r="E87">
-        <v>0.8946377383300461</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+        <v>0.89463773833004612</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>86</v>
       </c>
       <c r="B88">
-        <v>0.7439658119658119</v>
+        <v>0.74396581196581191</v>
       </c>
       <c r="C88">
         <v>1.213004860063684</v>
       </c>
       <c r="D88">
-        <v>20.91387689764971</v>
+        <v>20.913876897649711</v>
       </c>
       <c r="E88">
-        <v>0.9024341456357544</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <v>0.90243414563575441</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>87</v>
       </c>
       <c r="B89">
-        <v>0.7471794871794871</v>
+        <v>0.74717948717948712</v>
       </c>
       <c r="C89">
-        <v>1.205128205128205</v>
+        <v>1.2051282051282051</v>
       </c>
       <c r="D89">
-        <v>20.77807250221043</v>
+        <v>20.778072502210431</v>
       </c>
       <c r="E89">
-        <v>0.9004470742932282</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+        <v>0.90044707429322823</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -2087,239 +2217,239 @@
         <v>1.197251550192727</v>
       </c>
       <c r="D90">
-        <v>20.64226810677115</v>
+        <v>20.642268106771152</v>
       </c>
       <c r="E90">
         <v>0.9003331657449305</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>89</v>
       </c>
       <c r="B91">
-        <v>0.7568205128205128</v>
+        <v>0.75682051282051277</v>
       </c>
       <c r="C91">
         <v>1.189374895257248</v>
       </c>
       <c r="D91">
-        <v>20.50646371133186</v>
+        <v>20.506463711331861</v>
       </c>
       <c r="E91">
-        <v>0.9001433181644342</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
+        <v>0.90014331816443416</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>90</v>
       </c>
       <c r="B92">
-        <v>0.7616410256410256</v>
+        <v>0.76164102564102565</v>
       </c>
       <c r="C92">
         <v>1.189374895257248</v>
       </c>
       <c r="D92">
-        <v>20.50646371133186</v>
+        <v>20.506463711331861</v>
       </c>
       <c r="E92">
-        <v>0.9058767150954179</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
+        <v>0.90587671509541789</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>91</v>
       </c>
       <c r="B93">
-        <v>0.7664615384615384</v>
+        <v>0.76646153846153842</v>
       </c>
       <c r="C93">
         <v>1.173621585386291</v>
       </c>
       <c r="D93">
-        <v>20.2348549204533</v>
+        <v>20.234854920453301</v>
       </c>
       <c r="E93">
-        <v>0.8995358059068466</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
+        <v>0.89953580590684656</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>92</v>
       </c>
       <c r="B94">
-        <v>0.7696752136752137</v>
+        <v>0.76967521367521374</v>
       </c>
       <c r="C94">
         <v>1.165744930450813</v>
       </c>
       <c r="D94">
-        <v>20.09905052501401</v>
+        <v>20.099050525014011</v>
       </c>
       <c r="E94">
-        <v>0.8972449784355264</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
+        <v>0.89724497843552642</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>93</v>
       </c>
       <c r="B95">
-        <v>0.7744957264957265</v>
+        <v>0.77449572649572651</v>
       </c>
       <c r="C95">
         <v>1.165744930450813</v>
       </c>
       <c r="D95">
-        <v>20.09905052501401</v>
+        <v>20.099050525014011</v>
       </c>
       <c r="E95">
-        <v>0.9028644668182124</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
+        <v>0.90286446681821242</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>94</v>
       </c>
       <c r="B96">
-        <v>0.7777094017094017</v>
+        <v>0.77770940170940173</v>
       </c>
       <c r="C96">
         <v>1.157868275515334</v>
       </c>
       <c r="D96">
-        <v>19.96324612957473</v>
+        <v>19.963246129574731</v>
       </c>
       <c r="E96">
-        <v>0.9004850438093275</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
+        <v>0.90048504380932748</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>95</v>
       </c>
       <c r="B97">
-        <v>0.7809230769230769</v>
+        <v>0.78092307692307694</v>
       </c>
       <c r="C97">
         <v>1.157868275515334</v>
       </c>
       <c r="D97">
-        <v>19.96324612957473</v>
+        <v>19.963246129574731</v>
       </c>
       <c r="E97">
-        <v>0.904206056387052</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
+        <v>0.90420605638705198</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>96</v>
       </c>
       <c r="B98">
-        <v>0.7857435897435897</v>
+        <v>0.78574358974358971</v>
       </c>
       <c r="C98">
         <v>1.142114965644377</v>
       </c>
       <c r="D98">
-        <v>19.69163733869616</v>
+        <v>19.691637338696161</v>
       </c>
       <c r="E98">
-        <v>0.8974095130052897</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
+        <v>0.89740951300528971</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>97</v>
       </c>
       <c r="B99">
-        <v>0.7905641025641026</v>
+        <v>0.79056410256410259</v>
       </c>
       <c r="C99">
-        <v>1.126361655773421</v>
+        <v>1.1263616557734211</v>
       </c>
       <c r="D99">
-        <v>19.42002854781759</v>
+        <v>19.420028547817591</v>
       </c>
       <c r="E99">
-        <v>0.8904610915591309</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
+        <v>0.89046109155913089</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>98</v>
       </c>
       <c r="B100">
-        <v>0.7953846153846154</v>
+        <v>0.79538461538461536</v>
       </c>
       <c r="C100">
-        <v>1.110608345902463</v>
+        <v>1.1106083459024629</v>
       </c>
       <c r="D100">
         <v>19.14841975693902</v>
       </c>
       <c r="E100">
-        <v>0.8833607920485747</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
+        <v>0.88336079204857465</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>99</v>
       </c>
       <c r="B101">
-        <v>0.8002051282051282</v>
+        <v>0.80020512820512824</v>
       </c>
       <c r="C101">
-        <v>1.102731690966985</v>
+        <v>1.1027316909669851</v>
       </c>
       <c r="D101">
-        <v>19.01261536149974</v>
+        <v>19.012615361499741</v>
       </c>
       <c r="E101">
-        <v>0.8824115541460942</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
+        <v>0.88241155414609418</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>100</v>
       </c>
       <c r="B102">
-        <v>0.8034188034188035</v>
+        <v>0.80341880341880345</v>
       </c>
       <c r="C102">
         <v>1.094855036031507</v>
       </c>
       <c r="D102">
-        <v>18.87681096606046</v>
+        <v>18.876810966060461</v>
       </c>
       <c r="E102">
-        <v>0.879627122965484</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
+        <v>0.87962712296548395</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>101</v>
       </c>
       <c r="B103">
-        <v>0.8066324786324786</v>
+        <v>0.80663247863247856</v>
       </c>
       <c r="C103">
-        <v>1.086978381096028</v>
+        <v>1.0869783810960281</v>
       </c>
       <c r="D103">
         <v>18.74100657062117</v>
       </c>
       <c r="E103">
-        <v>0.876792065763408</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
+        <v>0.87679206576340796</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>102</v>
       </c>
       <c r="B104">
-        <v>0.8114529914529914</v>
+        <v>0.81145299145299143</v>
       </c>
       <c r="C104">
         <v>1.071225071225071</v>
@@ -2328,10 +2458,10 @@
         <v>18.4693977797426</v>
       </c>
       <c r="E104">
-        <v>0.8692487885650277</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
+        <v>0.86924878856502774</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -2345,10 +2475,10 @@
         <v>18.4693977797426</v>
       </c>
       <c r="E105">
-        <v>0.8709700732948595</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
+        <v>0.87097007329485954</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -2359,35 +2489,35 @@
         <v>1.055471761354114</v>
       </c>
       <c r="D106">
-        <v>18.19778898886404</v>
+        <v>18.197788988864041</v>
       </c>
       <c r="E106">
-        <v>0.8615536333022508</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
+        <v>0.86155363330225077</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>105</v>
       </c>
       <c r="B107">
-        <v>0.8194871794871795</v>
+        <v>0.81948717948717953</v>
       </c>
       <c r="C107">
         <v>1.055471761354114</v>
       </c>
       <c r="D107">
-        <v>18.19778898886404</v>
+        <v>18.197788988864041</v>
       </c>
       <c r="E107">
         <v>0.8649455767404487</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>106</v>
       </c>
       <c r="B108">
-        <v>0.8227008547008547</v>
+        <v>0.82270085470085474</v>
       </c>
       <c r="C108">
         <v>1.039718451483157</v>
@@ -2396,10 +2526,10 @@
         <v>17.92618019798547</v>
       </c>
       <c r="E108">
-        <v>0.8553772586834428</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
+        <v>0.85537725868344283</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -2407,38 +2537,38 @@
         <v>0.8243076923076923</v>
       </c>
       <c r="C109">
-        <v>1.031841796547679</v>
+        <v>1.0318417965476789</v>
       </c>
       <c r="D109">
         <v>17.79037580254619</v>
       </c>
       <c r="E109">
-        <v>0.8505551301388405</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
+        <v>0.85055513013884054</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>108</v>
       </c>
       <c r="B110">
-        <v>0.8275213675213675</v>
+        <v>0.82752136752136751</v>
       </c>
       <c r="C110">
-        <v>1.031841796547679</v>
+        <v>1.0318417965476789</v>
       </c>
       <c r="D110">
         <v>17.79037580254619</v>
       </c>
       <c r="E110">
-        <v>0.85387113454484</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
+        <v>0.85387113454483998</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>109</v>
       </c>
       <c r="B111">
-        <v>0.8291282051282052</v>
+        <v>0.82912820512820518</v>
       </c>
       <c r="C111">
         <v>1.0239651416122</v>
@@ -2447,44 +2577,44 @@
         <v>17.6545714071069</v>
       </c>
       <c r="E111">
-        <v>0.8489983799787721</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
+        <v>0.84899837997877214</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>110</v>
       </c>
       <c r="B112">
-        <v>0.8307350427350427</v>
+        <v>0.83073504273504273</v>
       </c>
       <c r="C112">
-        <v>1.016088486676722</v>
+        <v>1.0160884866767219</v>
       </c>
       <c r="D112">
         <v>17.51876701166762</v>
       </c>
       <c r="E112">
-        <v>0.8441003124019715</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
+        <v>0.84410031240197148</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>111</v>
       </c>
       <c r="B113">
-        <v>0.8323418803418804</v>
+        <v>0.83234188034188039</v>
       </c>
       <c r="C113">
-        <v>1.016088486676722</v>
+        <v>1.0160884866767219</v>
       </c>
       <c r="D113">
         <v>17.51876701166762</v>
       </c>
       <c r="E113">
-        <v>0.8457330015942384</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
+        <v>0.84573300159423836</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -2492,480 +2622,480 @@
         <v>0.8355555555555555</v>
       </c>
       <c r="C114">
-        <v>1.000335176805765</v>
+        <v>1.0003351768057649</v>
       </c>
       <c r="D114">
         <v>17.24715822078905</v>
       </c>
       <c r="E114">
-        <v>0.8358356143977057</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
+        <v>0.83583561439770571</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>113</v>
       </c>
       <c r="B115">
-        <v>0.8371623931623932</v>
+        <v>0.83716239316239316</v>
       </c>
       <c r="C115">
-        <v>0.9924585218702867</v>
+        <v>0.99245852187028671</v>
       </c>
       <c r="D115">
         <v>17.11135382534977</v>
       </c>
       <c r="E115">
-        <v>0.8308489512833406</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
+        <v>0.83084895128334058</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>114</v>
       </c>
       <c r="B116">
-        <v>0.8403760683760684</v>
+        <v>0.84037606837606837</v>
       </c>
       <c r="C116">
-        <v>0.984581866934808</v>
+        <v>0.98458186693480798</v>
       </c>
       <c r="D116">
         <v>16.97554942991048</v>
       </c>
       <c r="E116">
-        <v>0.8274190383290433</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
+        <v>0.82741903832904329</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>115</v>
       </c>
       <c r="B117">
-        <v>0.841982905982906</v>
+        <v>0.84198290598290604</v>
       </c>
       <c r="C117">
-        <v>0.9767052119993296</v>
+        <v>0.97670521199932958</v>
       </c>
       <c r="D117">
         <v>16.8397450344712</v>
       </c>
       <c r="E117">
-        <v>0.8223690926878459</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
+        <v>0.82236909268784586</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>116</v>
       </c>
       <c r="B118">
-        <v>0.8435897435897436</v>
+        <v>0.84358974358974359</v>
       </c>
       <c r="C118">
-        <v>0.9688285570638512</v>
+        <v>0.96882855706385118</v>
       </c>
       <c r="D118">
         <v>16.70394063903192</v>
       </c>
       <c r="E118">
-        <v>0.8172938340359155</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
+        <v>0.81729383403591549</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>117</v>
       </c>
       <c r="B119">
-        <v>0.8451965811965811</v>
+        <v>0.84519658119658114</v>
       </c>
       <c r="C119">
-        <v>0.9609519021283728</v>
+        <v>0.96095190212837278</v>
       </c>
       <c r="D119">
         <v>16.56813624359263</v>
       </c>
       <c r="E119">
-        <v>0.8121932623732523</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5">
+        <v>0.81219326237325229</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>118</v>
       </c>
       <c r="B120">
-        <v>0.8468034188034188</v>
+        <v>0.84680341880341881</v>
       </c>
       <c r="C120">
-        <v>0.9609519021283728</v>
+        <v>0.96095190212837278</v>
       </c>
       <c r="D120">
         <v>16.56813624359263</v>
       </c>
       <c r="E120">
-        <v>0.8137373560279544</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
+        <v>0.81373735602795438</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>119</v>
       </c>
       <c r="B121">
-        <v>0.8484102564102565</v>
+        <v>0.84841025641025647</v>
       </c>
       <c r="C121">
-        <v>0.9530752471928943</v>
+        <v>0.95307524719289427</v>
       </c>
       <c r="D121">
         <v>16.43233184815335</v>
       </c>
       <c r="E121">
-        <v>0.808598814849192</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
+        <v>0.80859881484919205</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>120</v>
       </c>
       <c r="B122">
-        <v>0.850017094017094</v>
+        <v>0.85001709401709402</v>
       </c>
       <c r="C122">
-        <v>0.9451985922574158</v>
+        <v>0.94519859225741576</v>
       </c>
       <c r="D122">
-        <v>16.29652745271406</v>
+        <v>16.296527452714059</v>
       </c>
       <c r="E122">
-        <v>0.8034349606596967</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
+        <v>0.80343496065969666</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>121</v>
       </c>
       <c r="B123">
-        <v>0.8516239316239317</v>
+        <v>0.85162393162393168</v>
       </c>
       <c r="C123">
-        <v>0.9373219373219374</v>
+        <v>0.93732193732193736</v>
       </c>
       <c r="D123">
         <v>16.16072305727478</v>
       </c>
       <c r="E123">
-        <v>0.7982457934594688</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5">
+        <v>0.79824579345946878</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>122</v>
       </c>
       <c r="B124">
-        <v>0.8532307692307692</v>
+        <v>0.85323076923076924</v>
       </c>
       <c r="C124">
-        <v>0.9373219373219374</v>
+        <v>0.93732193732193736</v>
       </c>
       <c r="D124">
         <v>16.16072305727478</v>
       </c>
       <c r="E124">
-        <v>0.7997519175980715</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
+        <v>0.79975191759807152</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>123</v>
       </c>
       <c r="B125">
-        <v>0.8548376068376068</v>
+        <v>0.85483760683760679</v>
       </c>
       <c r="C125">
-        <v>0.9294452823864588</v>
+        <v>0.92944528238645885</v>
       </c>
       <c r="D125">
         <v>16.0249186618355</v>
       </c>
       <c r="E125">
-        <v>0.7945247808817442</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5">
+        <v>0.79452478088174416</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>124</v>
       </c>
       <c r="B126">
-        <v>0.8548376068376068</v>
+        <v>0.85483760683760679</v>
       </c>
       <c r="C126">
-        <v>0.9294452823864588</v>
+        <v>0.92944528238645885</v>
       </c>
       <c r="D126">
         <v>16.0249186618355</v>
       </c>
       <c r="E126">
-        <v>0.7945247808817442</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
+        <v>0.79452478088174416</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>125</v>
       </c>
       <c r="B127">
-        <v>0.8564444444444445</v>
+        <v>0.85644444444444445</v>
       </c>
       <c r="C127">
-        <v>0.9215686274509803</v>
+        <v>0.92156862745098034</v>
       </c>
       <c r="D127">
-        <v>15.88911426639621</v>
+        <v>15.889114266396209</v>
       </c>
       <c r="E127">
-        <v>0.7892723311546841</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
+        <v>0.78927233115468409</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>126</v>
       </c>
       <c r="B128">
-        <v>0.8580512820512821</v>
+        <v>0.85805128205128212</v>
       </c>
       <c r="C128">
-        <v>0.9136919725155019</v>
+        <v>0.91369197251550194</v>
       </c>
       <c r="D128">
-        <v>15.75330987095693</v>
+        <v>15.753309870956929</v>
       </c>
       <c r="E128">
         <v>0.7839945684168913</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>127</v>
       </c>
       <c r="B129">
-        <v>0.8596581196581197</v>
+        <v>0.85965811965811967</v>
       </c>
       <c r="C129">
-        <v>0.9058153175800235</v>
+        <v>0.90581531758002354</v>
       </c>
       <c r="D129">
         <v>15.61750547551765</v>
       </c>
       <c r="E129">
-        <v>0.7786914926683656</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5">
+        <v>0.77869149266836557</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>128</v>
       </c>
       <c r="B130">
-        <v>0.8741196581196581</v>
+        <v>0.87411965811965808</v>
       </c>
       <c r="C130">
-        <v>0.7640355287414111</v>
+        <v>0.76403552874141112</v>
       </c>
       <c r="D130">
         <v>13.17302635761054</v>
       </c>
       <c r="E130">
-        <v>0.6678584751747145</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
+        <v>0.66785847517471453</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>129</v>
       </c>
       <c r="B131">
-        <v>0.8869743589743589</v>
+        <v>0.88697435897435895</v>
       </c>
       <c r="C131">
-        <v>0.6380090497737556</v>
+        <v>0.63800904977375561</v>
       </c>
       <c r="D131">
-        <v>11.00015603058199</v>
+        <v>11.000156030581991</v>
       </c>
       <c r="E131">
-        <v>0.5658976679429167</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
+        <v>0.56589766794291674</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>130</v>
       </c>
       <c r="B132">
-        <v>0.8982222222222223</v>
+        <v>0.89822222222222226</v>
       </c>
       <c r="C132">
-        <v>0.543489190548014</v>
+        <v>0.54348919054801403</v>
       </c>
       <c r="D132">
         <v>9.370503285310587</v>
       </c>
       <c r="E132">
-        <v>0.4881740684877939</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5">
+        <v>0.48817406848779388</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>131</v>
       </c>
       <c r="B133">
-        <v>0.9078632478632478</v>
+        <v>0.90786324786324779</v>
       </c>
       <c r="C133">
-        <v>0.456845986257751</v>
+        <v>0.45684598625775102</v>
       </c>
       <c r="D133">
-        <v>7.876654935478465</v>
+        <v>7.8766549354784647</v>
       </c>
       <c r="E133">
-        <v>0.4147536808572505</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
+        <v>0.41475368085725051</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>132</v>
       </c>
       <c r="B134">
-        <v>0.9158974358974359</v>
+        <v>0.91589743589743589</v>
       </c>
       <c r="C134">
-        <v>0.3938327467739232</v>
+        <v>0.39383274677392321</v>
       </c>
       <c r="D134">
-        <v>6.790219771964193</v>
+        <v>6.7902197719641926</v>
       </c>
       <c r="E134">
-        <v>0.3607104029426804</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
+        <v>0.36071040294268042</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>133</v>
       </c>
       <c r="B135">
-        <v>0.9223247863247863</v>
+        <v>0.92232478632478632</v>
       </c>
       <c r="C135">
-        <v>0.3308195072900955</v>
+        <v>0.33081950729009552</v>
       </c>
       <c r="D135">
-        <v>5.703784608449922</v>
+        <v>5.7037846084499222</v>
       </c>
       <c r="E135">
-        <v>0.3051230313734085</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
+        <v>0.30512303137340852</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>134</v>
       </c>
       <c r="B136">
-        <v>0.9287521367521369</v>
+        <v>0.92875213675213686</v>
       </c>
       <c r="C136">
-        <v>0.2756829227417463</v>
+        <v>0.27568292274174627</v>
       </c>
       <c r="D136">
-        <v>4.753153840374935</v>
+        <v>4.7531538403749352</v>
       </c>
       <c r="E136">
-        <v>0.2560411035624711</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
+        <v>0.25604110356247112</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>135</v>
       </c>
       <c r="B137">
-        <v>0.9335726495726496</v>
+        <v>0.93357264957264963</v>
       </c>
       <c r="C137">
-        <v>0.2362996480643539</v>
+        <v>0.23629964806435391</v>
       </c>
       <c r="D137">
-        <v>4.074131863178516</v>
+        <v>4.0741318631785157</v>
       </c>
       <c r="E137">
-        <v>0.2206028885365235</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5">
+        <v>0.22060288853652349</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>136</v>
       </c>
       <c r="B138">
-        <v>0.9383931623931625</v>
+        <v>0.93839316239316251</v>
       </c>
       <c r="C138">
-        <v>0.2047930283224401</v>
+        <v>0.20479302832244009</v>
       </c>
       <c r="D138">
         <v>3.530914281421381</v>
       </c>
       <c r="E138">
-        <v>0.1921763774835671</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5">
+        <v>0.19217637748356711</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>137</v>
       </c>
       <c r="B139">
-        <v>0.9416068376068376</v>
+        <v>0.94160683760683761</v>
       </c>
       <c r="C139">
-        <v>0.1732864085805262</v>
+        <v>0.17328640858052621</v>
       </c>
       <c r="D139">
-        <v>2.987696699664245</v>
+        <v>2.9876966996642449</v>
       </c>
       <c r="E139">
-        <v>0.1631676671837557</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
+        <v>0.16316766718375569</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>138</v>
       </c>
       <c r="B140">
-        <v>0.9464273504273504</v>
+        <v>0.94642735042735038</v>
       </c>
       <c r="C140">
-        <v>0.1496564437740908</v>
+        <v>0.14965644377409079</v>
       </c>
       <c r="D140">
-        <v>2.580283513346394</v>
+        <v>2.5802835133463939</v>
       </c>
       <c r="E140">
         <v>0.1416389515554925</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>139</v>
       </c>
       <c r="B141">
-        <v>0.948034188034188</v>
+        <v>0.94803418803418804</v>
       </c>
       <c r="C141">
-        <v>0.1260264789676555</v>
+        <v>0.12602647896765551</v>
       </c>
       <c r="D141">
-        <v>2.172870327028542</v>
+        <v>2.1728703270285421</v>
       </c>
       <c r="E141">
-        <v>0.1194774106589089</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5">
+        <v>0.11947741065890891</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>140</v>
       </c>
       <c r="B142">
-        <v>0.9512478632478633</v>
+        <v>0.95124786324786326</v>
       </c>
       <c r="C142">
         <v>0.1023965141612201</v>
@@ -2974,78 +3104,78 @@
         <v>1.76545714071069</v>
       </c>
       <c r="E142">
-        <v>0.09740446529989015</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
+        <v>9.740446529989015E-2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>141</v>
       </c>
       <c r="B143">
-        <v>0.9544615384615385</v>
+        <v>0.95446153846153847</v>
       </c>
       <c r="C143">
-        <v>0.08664320429026312</v>
+        <v>8.6643204290263121E-2</v>
       </c>
       <c r="D143">
-        <v>1.493848349832123</v>
+        <v>1.4938483498321229</v>
       </c>
       <c r="E143">
-        <v>0.08269760606412191</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
+        <v>8.2697606064121909E-2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>142</v>
       </c>
       <c r="B144">
-        <v>0.956068376068376</v>
+        <v>0.95606837606837602</v>
       </c>
       <c r="C144">
-        <v>0.07876654935478464</v>
+        <v>7.8766549354784637E-2</v>
       </c>
       <c r="D144">
         <v>1.358043954392838</v>
       </c>
       <c r="E144">
-        <v>0.07530620693013854</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
+        <v>7.5306206930138536E-2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>143</v>
       </c>
       <c r="B145">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C145">
-        <v>0.06301323948382773</v>
+        <v>6.3013239483827727E-2</v>
       </c>
       <c r="D145">
-        <v>1.086435163514271</v>
+        <v>1.0864351635142711</v>
       </c>
       <c r="E145">
-        <v>0.06034621758704213</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
+        <v>6.0346217587042131E-2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>144</v>
       </c>
       <c r="B146">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C146">
-        <v>0.05513658454834925</v>
+        <v>5.513658454834925E-2</v>
       </c>
       <c r="D146">
-        <v>0.950630768074987</v>
+        <v>0.95063076807498703</v>
       </c>
       <c r="E146">
-        <v>0.05289153592622672</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
+        <v>5.2891535926226717E-2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>145</v>
       </c>
@@ -3053,16 +3183,16 @@
         <v>0.9608888888888889</v>
       </c>
       <c r="C147">
-        <v>0.04725992961287079</v>
+        <v>4.7259929612870788E-2</v>
       </c>
       <c r="D147">
-        <v>0.8148263726357032</v>
+        <v>0.81482637263570323</v>
       </c>
       <c r="E147">
-        <v>0.04541154125467851</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
+        <v>4.5411541254678507E-2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>146</v>
       </c>
@@ -3070,169 +3200,169 @@
         <v>0.9608888888888889</v>
       </c>
       <c r="C148">
-        <v>0.03938327467739232</v>
+        <v>3.9383274677392319E-2</v>
       </c>
       <c r="D148">
-        <v>0.6790219771964192</v>
+        <v>0.67902197719641921</v>
       </c>
       <c r="E148">
-        <v>0.03784295104556542</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
+        <v>3.7842951045565419E-2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>147</v>
       </c>
       <c r="B149">
-        <v>0.9624957264957266</v>
+        <v>0.96249572649572657</v>
       </c>
       <c r="C149">
-        <v>0.03938327467739232</v>
+        <v>3.9383274677392319E-2</v>
       </c>
       <c r="D149">
-        <v>0.6790219771964192</v>
+        <v>0.67902197719641921</v>
       </c>
       <c r="E149">
-        <v>0.03790623357239747</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
+        <v>3.7906233572397467E-2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>148</v>
       </c>
       <c r="B150">
-        <v>0.9641025641025641</v>
+        <v>0.96410256410256412</v>
       </c>
       <c r="C150">
-        <v>0.03150661974191386</v>
+        <v>3.1506619741913863E-2</v>
       </c>
       <c r="D150">
-        <v>0.5432175817571355</v>
+        <v>0.54321758175713553</v>
       </c>
       <c r="E150">
-        <v>0.03037561287938362</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
+        <v>3.0375612879383621E-2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>149</v>
       </c>
       <c r="B151">
-        <v>0.9641025641025641</v>
+        <v>0.96410256410256412</v>
       </c>
       <c r="C151">
-        <v>0.02362996480643539</v>
+        <v>2.3629964806435391E-2</v>
       </c>
       <c r="D151">
-        <v>0.4074131863178516</v>
+        <v>0.40741318631785162</v>
       </c>
       <c r="E151">
-        <v>0.02278170965953771</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
+        <v>2.278170965953771E-2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>150</v>
       </c>
       <c r="B152">
-        <v>0.9657094017094017</v>
+        <v>0.96570940170940167</v>
       </c>
       <c r="C152">
-        <v>0.01575330987095693</v>
+        <v>1.5753309870956932E-2</v>
       </c>
       <c r="D152">
-        <v>0.2716087908785678</v>
+        <v>0.27160879087856782</v>
       </c>
       <c r="E152">
-        <v>0.01521311945042463</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
+        <v>1.5213119450424631E-2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>151</v>
       </c>
       <c r="B153">
-        <v>0.9657094017094017</v>
+        <v>0.96570940170940167</v>
       </c>
       <c r="C153">
-        <v>0.02362996480643539</v>
+        <v>2.3629964806435391E-2</v>
       </c>
       <c r="D153">
-        <v>0.4074131863178516</v>
+        <v>0.40741318631785162</v>
       </c>
       <c r="E153">
-        <v>0.02281967917563694</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5">
+        <v>2.2819679175636941E-2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>152</v>
       </c>
       <c r="B154">
-        <v>0.9657094017094017</v>
+        <v>0.96570940170940167</v>
       </c>
       <c r="C154">
-        <v>0.01575330987095693</v>
+        <v>1.5753309870956932E-2</v>
       </c>
       <c r="D154">
-        <v>0.2716087908785678</v>
+        <v>0.27160879087856782</v>
       </c>
       <c r="E154">
-        <v>0.01521311945042463</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
+        <v>1.5213119450424631E-2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>153</v>
       </c>
       <c r="B155">
-        <v>0.9673162393162393</v>
+        <v>0.96731623931623933</v>
       </c>
       <c r="C155">
-        <v>0.01575330987095693</v>
+        <v>1.5753309870956932E-2</v>
       </c>
       <c r="D155">
-        <v>0.2716087908785678</v>
+        <v>0.27160879087856782</v>
       </c>
       <c r="E155">
-        <v>0.01523843246115745</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5">
+        <v>1.523843246115745E-2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>154</v>
       </c>
       <c r="B156">
-        <v>0.9673162393162393</v>
+        <v>0.96731623931623933</v>
       </c>
       <c r="C156">
-        <v>0.01575330987095693</v>
+        <v>1.5753309870956932E-2</v>
       </c>
       <c r="D156">
-        <v>0.2716087908785678</v>
+        <v>0.27160879087856782</v>
       </c>
       <c r="E156">
-        <v>0.01523843246115745</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5">
+        <v>1.523843246115745E-2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>155</v>
       </c>
       <c r="B157">
-        <v>0.9673162393162393</v>
+        <v>0.96731623931623933</v>
       </c>
       <c r="C157">
-        <v>0.01575330987095693</v>
+        <v>1.5753309870956932E-2</v>
       </c>
       <c r="D157">
-        <v>0.2716087908785678</v>
+        <v>0.27160879087856782</v>
       </c>
       <c r="E157">
-        <v>0.01523843246115745</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5">
+        <v>1.523843246115745E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>156</v>
       </c>
@@ -3240,16 +3370,16 @@
         <v>0.968923076923077</v>
       </c>
       <c r="C158">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D158">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E158">
-        <v>0.007631872735945136</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5">
+        <v>7.631872735945136E-3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>157</v>
       </c>
@@ -3257,16 +3387,16 @@
         <v>0.968923076923077</v>
       </c>
       <c r="C159">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D159">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E159">
-        <v>0.007631872735945136</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5">
+        <v>7.631872735945136E-3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>158</v>
       </c>
@@ -3274,16 +3404,16 @@
         <v>0.968923076923077</v>
       </c>
       <c r="C160">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D160">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E160">
-        <v>0.007631872735945136</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5">
+        <v>7.631872735945136E-3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>159</v>
       </c>
@@ -3291,123 +3421,123 @@
         <v>0.968923076923077</v>
       </c>
       <c r="C161">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D161">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E161">
-        <v>0.007631872735945136</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5">
+        <v>7.631872735945136E-3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>160</v>
       </c>
       <c r="B162">
-        <v>0.9705299145299146</v>
+        <v>0.97052991452991455</v>
       </c>
       <c r="C162">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D162">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E162">
-        <v>0.007644529241311545</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5">
+        <v>7.6445292413115451E-3</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>161</v>
       </c>
       <c r="B163">
-        <v>0.9705299145299146</v>
+        <v>0.97052991452991455</v>
       </c>
       <c r="C163">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D163">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E163">
-        <v>0.007644529241311545</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5">
+        <v>7.6445292413115451E-3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>162</v>
       </c>
       <c r="B164">
-        <v>0.9705299145299146</v>
+        <v>0.97052991452991455</v>
       </c>
       <c r="C164">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D164">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E164">
-        <v>0.007644529241311545</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5">
+        <v>7.6445292413115451E-3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>163</v>
       </c>
       <c r="B165">
-        <v>0.9705299145299146</v>
+        <v>0.97052991452991455</v>
       </c>
       <c r="C165">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D165">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E165">
-        <v>0.007644529241311545</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5">
+        <v>7.6445292413115451E-3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>164</v>
       </c>
       <c r="B166">
-        <v>0.9705299145299146</v>
+        <v>0.97052991452991455</v>
       </c>
       <c r="C166">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D166">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E166">
-        <v>0.007644529241311545</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5">
+        <v>7.6445292413115451E-3</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>165</v>
       </c>
       <c r="B167">
-        <v>0.9705299145299146</v>
+        <v>0.97052991452991455</v>
       </c>
       <c r="C167">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D167">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E167">
-        <v>0.007644529241311545</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5">
+        <v>7.6445292413115451E-3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>166</v>
       </c>
       <c r="B168">
-        <v>0.9705299145299146</v>
+        <v>0.97052991452991455</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3419,46 +3549,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>167</v>
       </c>
       <c r="B169">
-        <v>0.9705299145299146</v>
+        <v>0.97052991452991455</v>
       </c>
       <c r="C169">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D169">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E169">
-        <v>0.007644529241311545</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5">
+        <v>7.6445292413115451E-3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>168</v>
       </c>
       <c r="B170">
-        <v>0.9721367521367522</v>
+        <v>0.97213675213675221</v>
       </c>
       <c r="C170">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D170">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E170">
-        <v>0.007657185746677955</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5">
+        <v>7.6571857466779551E-3</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>169</v>
       </c>
       <c r="B171">
-        <v>0.9721367521367522</v>
+        <v>0.97213675213675221</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3470,12 +3600,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>170</v>
       </c>
       <c r="B172">
-        <v>0.9721367521367522</v>
+        <v>0.97213675213675221</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -3487,12 +3617,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>171</v>
       </c>
       <c r="B173">
-        <v>0.9721367521367522</v>
+        <v>0.97213675213675221</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3504,12 +3634,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>172</v>
       </c>
       <c r="B174">
-        <v>0.9721367521367522</v>
+        <v>0.97213675213675221</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3521,12 +3651,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>173</v>
       </c>
       <c r="B175">
-        <v>0.9721367521367522</v>
+        <v>0.97213675213675221</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3538,29 +3668,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>174</v>
       </c>
       <c r="B176">
-        <v>0.9721367521367522</v>
+        <v>0.97213675213675221</v>
       </c>
       <c r="C176">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D176">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E176">
-        <v>0.007657185746677955</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5">
+        <v>7.6571857466779551E-3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>175</v>
       </c>
       <c r="B177">
-        <v>0.9721367521367522</v>
+        <v>0.97213675213675221</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3572,12 +3702,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>176</v>
       </c>
       <c r="B178">
-        <v>0.9721367521367522</v>
+        <v>0.97213675213675221</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3589,12 +3719,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>177</v>
       </c>
       <c r="B179">
-        <v>0.9721367521367522</v>
+        <v>0.97213675213675221</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -3606,12 +3736,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>178</v>
       </c>
       <c r="B180">
-        <v>0.9721367521367522</v>
+        <v>0.97213675213675221</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -3623,12 +3753,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>179</v>
       </c>
       <c r="B181">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -3640,12 +3770,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>180</v>
       </c>
       <c r="B182">
-        <v>0.9721367521367522</v>
+        <v>0.97213675213675221</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -3657,12 +3787,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>181</v>
       </c>
       <c r="B183">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -3674,12 +3804,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>182</v>
       </c>
       <c r="B184">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -3691,12 +3821,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>183</v>
       </c>
       <c r="B185">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -3708,12 +3838,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>184</v>
       </c>
       <c r="B186">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -3725,12 +3855,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>185</v>
       </c>
       <c r="B187">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -3742,12 +3872,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>186</v>
       </c>
       <c r="B188">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -3759,12 +3889,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>187</v>
       </c>
       <c r="B189">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -3776,12 +3906,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>188</v>
       </c>
       <c r="B190">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -3793,12 +3923,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>189</v>
       </c>
       <c r="B191">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -3810,12 +3940,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>190</v>
       </c>
       <c r="B192">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -3827,12 +3957,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>191</v>
       </c>
       <c r="B193">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -3844,12 +3974,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>192</v>
       </c>
       <c r="B194">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C194">
         <v>0</v>
@@ -3861,12 +3991,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>193</v>
       </c>
       <c r="B195">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -3878,12 +4008,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>194</v>
       </c>
       <c r="B196">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -3895,12 +4025,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>195</v>
       </c>
       <c r="B197">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -3912,12 +4042,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>196</v>
       </c>
       <c r="B198">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -3929,12 +4059,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>197</v>
       </c>
       <c r="B199">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -3946,12 +4076,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>198</v>
       </c>
       <c r="B200">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -3963,12 +4093,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>199</v>
       </c>
       <c r="B201">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -3980,12 +4110,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>200</v>
       </c>
       <c r="B202">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -3997,12 +4127,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>201</v>
       </c>
       <c r="B203">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -4014,12 +4144,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>202</v>
       </c>
       <c r="B204">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -4031,12 +4161,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>203</v>
       </c>
       <c r="B205">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -4048,12 +4178,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>204</v>
       </c>
       <c r="B206">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -4065,12 +4195,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>205</v>
       </c>
       <c r="B207">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -4082,12 +4212,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:5">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>206</v>
       </c>
       <c r="B208">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -4099,12 +4229,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>207</v>
       </c>
       <c r="B209">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -4116,12 +4246,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>208</v>
       </c>
       <c r="B210">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -4133,12 +4263,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>209</v>
       </c>
       <c r="B211">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -4150,12 +4280,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>210</v>
       </c>
       <c r="B212">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -4167,12 +4297,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>211</v>
       </c>
       <c r="B213">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -4184,12 +4314,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>212</v>
       </c>
       <c r="B214">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -4201,12 +4331,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>213</v>
       </c>
       <c r="B215">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -4218,12 +4348,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>214</v>
       </c>
       <c r="B216">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -4235,12 +4365,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>215</v>
       </c>
       <c r="B217">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -4252,12 +4382,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>216</v>
       </c>
       <c r="B218">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C218">
         <v>0</v>
@@ -4269,12 +4399,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>217</v>
       </c>
       <c r="B219">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C219">
         <v>0</v>
@@ -4286,12 +4416,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>218</v>
       </c>
       <c r="B220">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -4303,12 +4433,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>219</v>
       </c>
       <c r="B221">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -4320,12 +4450,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>220</v>
       </c>
       <c r="B222">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -4337,12 +4467,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>221</v>
       </c>
       <c r="B223">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C223">
         <v>0</v>
@@ -4354,12 +4484,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>222</v>
       </c>
       <c r="B224">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C224">
         <v>0</v>
@@ -4371,12 +4501,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:5">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>223</v>
       </c>
       <c r="B225">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -4388,12 +4518,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:5">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>224</v>
       </c>
       <c r="B226">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -4405,12 +4535,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:5">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>225</v>
       </c>
       <c r="B227">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -4422,12 +4552,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:5">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>226</v>
       </c>
       <c r="B228">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C228">
         <v>0</v>
@@ -4439,12 +4569,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:5">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>227</v>
       </c>
       <c r="B229">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C229">
         <v>0</v>
@@ -4456,12 +4586,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:5">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>228</v>
       </c>
       <c r="B230">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -4473,12 +4603,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:5">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>229</v>
       </c>
       <c r="B231">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -4490,12 +4620,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:5">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>230</v>
       </c>
       <c r="B232">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C232">
         <v>0</v>
@@ -4507,12 +4637,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:5">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>231</v>
       </c>
       <c r="B233">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -4524,12 +4654,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:5">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>232</v>
       </c>
       <c r="B234">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C234">
         <v>0</v>
@@ -4541,12 +4671,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:5">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>233</v>
       </c>
       <c r="B235">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C235">
         <v>0</v>
@@ -4558,12 +4688,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:5">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>234</v>
       </c>
       <c r="B236">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -4575,12 +4705,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:5">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>235</v>
       </c>
       <c r="B237">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -4592,12 +4722,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:5">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>236</v>
       </c>
       <c r="B238">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -4609,12 +4739,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:5">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>237</v>
       </c>
       <c r="B239">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C239">
         <v>0</v>
@@ -4626,12 +4756,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:5">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>238</v>
       </c>
       <c r="B240">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C240">
         <v>0</v>
@@ -4643,12 +4773,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:5">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>239</v>
       </c>
       <c r="B241">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -4660,12 +4790,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:5">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>240</v>
       </c>
       <c r="B242">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C242">
         <v>0</v>
@@ -4677,12 +4807,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:5">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
         <v>241</v>
       </c>
       <c r="B243">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C243">
         <v>0</v>
@@ -4694,12 +4824,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:5">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A244" s="1">
         <v>242</v>
       </c>
       <c r="B244">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C244">
         <v>0</v>
@@ -4711,12 +4841,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:5">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A245" s="1">
         <v>243</v>
       </c>
       <c r="B245">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C245">
         <v>0</v>
@@ -4728,12 +4858,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:5">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
         <v>244</v>
       </c>
       <c r="B246">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -4745,12 +4875,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:5">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
         <v>245</v>
       </c>
       <c r="B247">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C247">
         <v>0</v>
@@ -4762,12 +4892,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:5">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A248" s="1">
         <v>246</v>
       </c>
       <c r="B248">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C248">
         <v>0</v>
@@ -4779,12 +4909,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:5">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A249" s="1">
         <v>247</v>
       </c>
       <c r="B249">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C249">
         <v>0</v>
@@ -4796,12 +4926,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:5">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A250" s="1">
         <v>248</v>
       </c>
       <c r="B250">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C250">
         <v>0</v>
@@ -4813,12 +4943,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:5">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A251" s="1">
         <v>249</v>
       </c>
       <c r="B251">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C251">
         <v>0</v>
@@ -4830,12 +4960,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:5">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
         <v>250</v>
       </c>
       <c r="B252">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C252">
         <v>0</v>
@@ -4847,12 +4977,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:5">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>251</v>
       </c>
       <c r="B253">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C253">
         <v>0</v>
@@ -4864,12 +4994,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:5">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>252</v>
       </c>
       <c r="B254">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C254">
         <v>0</v>
@@ -4881,12 +5011,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:5">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A255" s="1">
         <v>253</v>
       </c>
       <c r="B255">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C255">
         <v>0</v>
@@ -4898,12 +5028,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:5">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A256" s="1">
         <v>254</v>
       </c>
       <c r="B256">
-        <v>0.9737435897435898</v>
+        <v>0.97374358974358977</v>
       </c>
       <c r="C256">
         <v>0</v>
@@ -4915,12 +5045,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:5">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A257" s="1">
         <v>255</v>
       </c>
       <c r="B257">
-        <v>0.9753504273504273</v>
+        <v>0.97535042735042732</v>
       </c>
       <c r="C257">
         <v>0</v>
